--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,34 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +60,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,38 +454,1422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Document_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scheduled_Sale_Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Court_Filing_Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Document_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Direct_Court_Record_Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7140</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2027</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNHHz3SozCezeRI2vkUwy0uiwMMZgibq59cy5K785CrTEMyPDsOYmCTVP5hyJkJU1bO1o58n6s0lxLJ6oof59ghK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7828</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>04/06/2027</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNEl7qNJ4CvE/0NueJ+S4zQbSfu2WEyrasTwYMPoMONyYc4iYReJs3flAKNtLYjrae3IOgaCjo1MuFMLICB8c3mH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7052</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2027</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>09/24/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyu7kQJKvj6WB4WOjyk7WprD5SOwNnavLkbHE46ioV+wWkcJDdPr+FVHUVabA40RI5HoTZAsK7vmoNl8pjS25eso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-6803</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>02/02/2027</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>09/15/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqWQ0Frk50yWO27qHp80a9/7vLSfK1ixIiiQcszcEiu7i0N3bEcqRx7p7Bh4sZTvPfAu3gmsvPuIyNK99yeXoK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7815</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2027</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRbotgUHdJzWLhBp0DwBcc/+3Dk8F8qG7Mp5JbE6d2FihjiMuJ4dKRbeuzoh3/pOjF+4WTCacCWrYO/Db+V4OLw</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-4751</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTvnvI5i1EaYEHYE9IUM9gBwJ81IYSOdvvwehObd3nXphm0Omf5bxwz05bsGeBZndJFBLgzPGCeA/BCFAIlY45+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-6402</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jytWfj882gWXL/+/9I5LXvTUb8ioTA8d7wWc2fNIo3Xtox7VOAa1k4RB0C48z7IRtD6dqDU25S5ILoKYYkZLOFIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7181</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSz8TQyjykaScwy4MXDzjWoI9O/eB/FRNb9gTzJHoJAi0liU1gyQd+nSZU5bwWbpC7wd4p0fGzxxsddPZ1OPhZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7408</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS5tEjapY60kBilva8st2XiTrjq4OHpdP5I4sz742b41bO6fl/yLegtLra9/oMx6RpzyhzRLvTjdCy/RYosvObA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7409</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSxvmP9INW4q9N5y6gDYVU14NM5XruBd/g19nJu+XiIvN+BYhup340S3JRDCv1sbstvTADur/T5WfCjpEXdYkU9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7410</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRIdL4OwFbCyUHSMpRz/cEzas+ndb/wm6JRRfCH2qiBI2sNbYfDi5Kz8gfzvPLqNSGZABPl4ImwnHgL5yd7nYmj</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7423</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqF2nHwQs4OGbG8NV0fSdm5Eim2T7qwwTliFofvDzStivCXpHpi4Os7YSk2P4bTgh7Bi5mwgBrE+iZgV6JNnZ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7424</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuCBQTxEriTYJIKp3x9TacrZntm2B3XO44wXehJQQ7GEYjwzezChnqGn+KP3vp0MUVdKFmgBmuKNeTCFRWO97mz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7425</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuG7uViEw7pLPVNcTN6jDDPepl6i/ph6p9jkYCFBD8/ibMRiRGtuFSorFjBj9JS8r/9KAuQIx1gkOUwZPjuUf30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7426</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyv+SWiDKaitm6RC0ggXxSGrJCOhGQefO8xMkjY+BuJcl1S0yCbHhM38IIEhg4xWzNsq6X1tj4zLkyv29b9ApNAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7430</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEFYQj99dHPPiUi1qvasfwHFWOixuTkN5HXVjxPgNzO0VEqYAQZciUwy5WShec7lCQ4L08Vpa7gGEhExB9BOm6S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7472</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5bZnWnkDFllWSZ2E4Y+Hc48KO0Bly9KsxPNqC6YYFPpPRHVcRvJpER8e13zcb8ziafDm325KButdfUS++gHFQ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7473</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4awvONf5MaBdKV+k8h8tjZbmHo5Vne0P234XdqxQrSrrEVmerHY+Gv8bbZ5lpj0Hlbu7ZNGNoUhXNqjz0JKKOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7474</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC76tl4EO6VaOT0w8CHAtQGs8gI0wm9LvYzHc1gEaXSsZcqiYkE/1oCJA2B8wrOIepaVROl51g+/S5oixeGJFBXb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7475</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5fKsOExZKATTOGO2Xa1FMfv5snc6mCNUU1hKXBLAZC0PS7nNvUEyUPIL94LDx0U6fmxUgcHgcpvzwq9igtt9nG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7476</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6PReqMK/LFFkCchf3WXUA2ag+a609SCwXUn4EtAJeAF7OhruCjorCePVpb3dei5tYtXFVhPYRX4eN80Ukmvyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7477</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7gLgnQ/iiFa6Jcw39zjw8UGMLfR39RzlUvqfCnW4pMshOyMwy2NJ+zkWifRAY+SNt+Luu0//oeGPxeBdqasrs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7543</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuJqL36h/Obpu0k05p8tk7IWm3/x/7bKOxBUVoTcA5SCoAi3iJzVM8UjU8Gy38hSJfcBr/cHsbLG7clx134Llgq</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7544</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvkIoAmjHBWhI5xNONjN9YEHgNWXK/Xw2jYc0CVulG57HpZfUH64y3GfvOXo837V3uwWHG9IOH+29+As1Kf0MrU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7559</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4xATPb6L7Qx8GIgOuR09E99FdulkT+Xl0R01utj+4JD0gFi0sXUyUAmn3xM8fmjMLE2LXCFgWt1D+UloJik/FY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7614</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7iD7qPRLGVgyxHLgDDQBezYUcholOOauNEzOprNCLEw/Lda9kYZzKGkeJrhqBRQdHrDs4dhgInPN2P4zvN3g5K</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7627</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEz3dLbd4QiV3hetAg1x/5tCrNyvdv76iL7S7iW6hrSpMx0B5gRrbNEsOHRHpOhVwivZoF/HsLk9wJ6DO4qr/s1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7628</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyFvqboZo8Pr2fm12+E+jyi/ZrpeyychtDdak9PyUZ9XrTLzJtEPVm3F2Pi6iLBjRyALgmeSCQ28nvlg1LFLOZql</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7621</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jysdRNQpEB1hDuzfGy49nG35z/Zhl+GDIJFs3MEQ28RAXhkCtrGPg1M8KQdd+LBc87aScLKiEcyJXsViT86t15+D</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7622</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jys3T8xW8icUmFia0CD+JBdf805d1N57A8gPRzkxN6ZzG9V/a3UZp03R1nTxtu1g4mQWgPBkpZBNR38gebcl8bni</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7639</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS1SQ44IftPUOeXtDGcEbB0EU0LAPCJOy+g461t4JdEYiFHXaFbGD58Yvkt5ZQpx4QG7MpLHMFVAtgJpFNeOMuy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7640</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSjY3vMhVP+Xcc1KpbUWMQZcspSBoUbYtUA9xaEcRyXUkQ4CDqaBPhPE027DImKXKKn8CJS5mPntDKu6fBr0DVo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7649</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTI8YP9ywg8e7M1cXE89bchaBb6zHPCLMRTqTA4/+/eYUtxtomPw+rX/v+OCWvHbAW7nUJE+vuAmetv/wf3tv3Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7650</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQcewt+2sIpU+KGhf4iMhlFLSKtnRpefg6fVEhTB/s/USLXiWvesYj2OkzQP2Xyi/iTLDFbuvjbhfZ9yaIHb1Uf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7651</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQL3uqSjem7KtfPi+nDhgP+3tPH4ZNBxAb4Ge+JTCdWsms/qSU2CRdAoP679MmVheOoQOmukE0z6nWolbio6s4K</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7654</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVReb8DtEbqsPg68R8vu0tAXwb0XCQyQqxv1ECBQCdeFH+F52PFz/EK1iJI07wb1IyMRyY6qXkGyf11q1Fn98mBv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7756</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7RyRMKjpG27qrRxBcDQq8JNwIQlcXxoi0jlxs/XK6FQbr4YmHsOlP4alB/cjCHT4ngQiDG9k5EdPHoiq3tgOhe</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7762</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC74AlRJFmXW60+pXuQvgdDX5dOwUNV2S7GwYjvm2x255yUgWNrno/DWumxR51giPSa3Qm2iYpVG+/OJktxXC2T0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7763</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7SPaa6ekl5UN2duI/XORrn58ypEnhgOrJaJlR4EBC4HkbOJo4eDN1m4vM4IN0RiHBd0EM/owsZfviFztShOSme</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7764</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5J3iNGA2ZkldcU8Li9NVCRavga8mzTDfR/zJh2ufG/E8IJjg4bjEmt0vUX7a2Q1oZwIxWwq3G/LYOkKyxQRoDi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7765</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6zdDf6uiq3hn30j56s3jsSu7o6TJ/dM3toCMGB7ODysPqCjB9BPnG+ZBbmNXhvHC+m3HEqT6cqsZQF7wJwSzJa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7766</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC58Rzz0Due88sAHNlFFvP0ayFCHCzHp3Eq4vuDEByVJMkow+2VXAxf1U8uo7tXbeCLWld4XVhS+f1L389A3HDxe</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7767</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6FI/LukdRpLllLexuFK+QgjsinEvvcaDIVK0XF3jqjtSl81RmZzMX1lq8VN/6DvowPSNjUYBXxAXIWvOfegtEh</t>
         </is>
       </c>
     </row>

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -596,17 +596,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-6803</t>
+          <t>FRCL-2026-7999</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>02/02/2027</t>
+          <t>03/02/2027</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>10/22/2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -621,14 +621,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqWQ0Frk50yWO27qHp80a9/7vLSfK1ixIiiQcszcEiu7i0N3bEcqRx7p7Bh4sZTvPfAu3gmsvPuIyNK99yeXoK</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvY/7ZQnmZIG+2sIB5azcMp4rDQLRo6h240EYwzj05BrPujAiTt2SEIXn5nu+fpZWF+gaf3Giwbf/fGZv4kbZ/T</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7815</t>
+          <t>FRCL-2026-6803</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10/15/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -653,24 +653,24 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRbotgUHdJzWLhBp0DwBcc/+3Dk8F8qG7Mp5JbE6d2FihjiMuJ4dKRbeuzoh3/pOjF+4WTCacCWrYO/Db+V4OLw</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqWQ0Frk50yWO27qHp80a9/7vLSfK1ixIiiQcszcEiu7i0N3bEcqRx7p7Bh4sZTvPfAu3gmsvPuIyNK99yeXoK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-4751</t>
+          <t>FRCL-2026-7815</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>01/05/2027</t>
+          <t>02/02/2027</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>10/15/2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -685,24 +685,27 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTvnvI5i1EaYEHYE9IUM9gBwJ81IYSOdvvwehObd3nXphm0Omf5bxwz05bsGeBZndJFBLgzPGCeA/BCFAIlY45+</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRbotgUHdJzWLhBp0DwBcc/+3Dk8F8qG7Mp5JbE6d2FihjiMuJ4dKRbeuzoh3/pOjF+4WTCacCWrYO/Db+V4OLw</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-6402</t>
+          <t>1
+2
+3
+4</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>01/05/2027</t>
+          <t>2027/1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>10/23/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -717,14 +720,14 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jytWfj882gWXL/+/9I5LXvTUb8ioTA8d7wWc2fNIo3Xtox7VOAa1k4RB0C48z7IRtD6dqDU25S5ILoKYYkZLOFIS</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/javascript:__doPostBack('ctl00$ContentPlaceHolder1$GridView1','Page$2')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7181</t>
+          <t>FRCL-2026-4751</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -734,7 +737,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -749,14 +752,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSz8TQyjykaScwy4MXDzjWoI9O/eB/FRNb9gTzJHoJAi0liU1gyQd+nSZU5bwWbpC7wd4p0fGzxxsddPZ1OPhZr</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTvnvI5i1EaYEHYE9IUM9gBwJ81IYSOdvvwehObd3nXphm0Omf5bxwz05bsGeBZndJFBLgzPGCeA/BCFAIlY45+</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7408</t>
+          <t>FRCL-2026-6402</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -766,7 +769,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -781,14 +784,14 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS5tEjapY60kBilva8st2XiTrjq4OHpdP5I4sz742b41bO6fl/yLegtLra9/oMx6RpzyhzRLvTjdCy/RYosvObA</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jytWfj882gWXL/+/9I5LXvTUb8ioTA8d7wWc2fNIo3Xtox7VOAa1k4RB0C48z7IRtD6dqDU25S5ILoKYYkZLOFIS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7409</t>
+          <t>FRCL-2026-7181</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -798,7 +801,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>09/29/2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -813,14 +816,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSxvmP9INW4q9N5y6gDYVU14NM5XruBd/g19nJu+XiIvN+BYhup340S3JRDCv1sbstvTADur/T5WfCjpEXdYkU9</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSz8TQyjykaScwy4MXDzjWoI9O/eB/FRNb9gTzJHoJAi0liU1gyQd+nSZU5bwWbpC7wd4p0fGzxxsddPZ1OPhZr</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7410</t>
+          <t>FRCL-2026-7408</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -845,14 +848,14 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRIdL4OwFbCyUHSMpRz/cEzas+ndb/wm6JRRfCH2qiBI2sNbYfDi5Kz8gfzvPLqNSGZABPl4ImwnHgL5yd7nYmj</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS5tEjapY60kBilva8st2XiTrjq4OHpdP5I4sz742b41bO6fl/yLegtLra9/oMx6RpzyhzRLvTjdCy/RYosvObA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7423</t>
+          <t>FRCL-2026-7409</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -877,14 +880,14 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqF2nHwQs4OGbG8NV0fSdm5Eim2T7qwwTliFofvDzStivCXpHpi4Os7YSk2P4bTgh7Bi5mwgBrE+iZgV6JNnZ5</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSxvmP9INW4q9N5y6gDYVU14NM5XruBd/g19nJu+XiIvN+BYhup340S3JRDCv1sbstvTADur/T5WfCjpEXdYkU9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7424</t>
+          <t>FRCL-2026-7410</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -909,14 +912,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuCBQTxEriTYJIKp3x9TacrZntm2B3XO44wXehJQQ7GEYjwzezChnqGn+KP3vp0MUVdKFmgBmuKNeTCFRWO97mz</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRIdL4OwFbCyUHSMpRz/cEzas+ndb/wm6JRRfCH2qiBI2sNbYfDi5Kz8gfzvPLqNSGZABPl4ImwnHgL5yd7nYmj</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7425</t>
+          <t>FRCL-2026-7423</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -941,14 +944,14 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuG7uViEw7pLPVNcTN6jDDPepl6i/ph6p9jkYCFBD8/ibMRiRGtuFSorFjBj9JS8r/9KAuQIx1gkOUwZPjuUf30</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqF2nHwQs4OGbG8NV0fSdm5Eim2T7qwwTliFofvDzStivCXpHpi4Os7YSk2P4bTgh7Bi5mwgBrE+iZgV6JNnZ5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7426</t>
+          <t>FRCL-2026-7424</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -973,14 +976,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyv+SWiDKaitm6RC0ggXxSGrJCOhGQefO8xMkjY+BuJcl1S0yCbHhM38IIEhg4xWzNsq6X1tj4zLkyv29b9ApNAO</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuCBQTxEriTYJIKp3x9TacrZntm2B3XO44wXehJQQ7GEYjwzezChnqGn+KP3vp0MUVdKFmgBmuKNeTCFRWO97mz</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7430</t>
+          <t>FRCL-2026-7425</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1005,14 +1008,14 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEFYQj99dHPPiUi1qvasfwHFWOixuTkN5HXVjxPgNzO0VEqYAQZciUwy5WShec7lCQ4L08Vpa7gGEhExB9BOm6S</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuG7uViEw7pLPVNcTN6jDDPepl6i/ph6p9jkYCFBD8/ibMRiRGtuFSorFjBj9JS8r/9KAuQIx1gkOUwZPjuUf30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7472</t>
+          <t>FRCL-2026-7426</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1037,14 +1040,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5bZnWnkDFllWSZ2E4Y+Hc48KO0Bly9KsxPNqC6YYFPpPRHVcRvJpER8e13zcb8ziafDm325KButdfUS++gHFQ2</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyv+SWiDKaitm6RC0ggXxSGrJCOhGQefO8xMkjY+BuJcl1S0yCbHhM38IIEhg4xWzNsq6X1tj4zLkyv29b9ApNAO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7473</t>
+          <t>FRCL-2026-7430</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1069,14 +1072,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4awvONf5MaBdKV+k8h8tjZbmHo5Vne0P234XdqxQrSrrEVmerHY+Gv8bbZ5lpj0Hlbu7ZNGNoUhXNqjz0JKKOB</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEFYQj99dHPPiUi1qvasfwHFWOixuTkN5HXVjxPgNzO0VEqYAQZciUwy5WShec7lCQ4L08Vpa7gGEhExB9BOm6S</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7474</t>
+          <t>FRCL-2026-7472</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1101,14 +1104,14 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC76tl4EO6VaOT0w8CHAtQGs8gI0wm9LvYzHc1gEaXSsZcqiYkE/1oCJA2B8wrOIepaVROl51g+/S5oixeGJFBXb</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5bZnWnkDFllWSZ2E4Y+Hc48KO0Bly9KsxPNqC6YYFPpPRHVcRvJpER8e13zcb8ziafDm325KButdfUS++gHFQ2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7475</t>
+          <t>FRCL-2026-7473</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1133,14 +1136,14 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5fKsOExZKATTOGO2Xa1FMfv5snc6mCNUU1hKXBLAZC0PS7nNvUEyUPIL94LDx0U6fmxUgcHgcpvzwq9igtt9nG</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4awvONf5MaBdKV+k8h8tjZbmHo5Vne0P234XdqxQrSrrEVmerHY+Gv8bbZ5lpj0Hlbu7ZNGNoUhXNqjz0JKKOB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7476</t>
+          <t>FRCL-2026-7474</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1165,14 +1168,14 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6PReqMK/LFFkCchf3WXUA2ag+a609SCwXUn4EtAJeAF7OhruCjorCePVpb3dei5tYtXFVhPYRX4eN80Ukmvyn/</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC76tl4EO6VaOT0w8CHAtQGs8gI0wm9LvYzHc1gEaXSsZcqiYkE/1oCJA2B8wrOIepaVROl51g+/S5oixeGJFBXb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7477</t>
+          <t>FRCL-2026-7475</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1197,14 +1200,14 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7gLgnQ/iiFa6Jcw39zjw8UGMLfR39RzlUvqfCnW4pMshOyMwy2NJ+zkWifRAY+SNt+Luu0//oeGPxeBdqasrs/</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5fKsOExZKATTOGO2Xa1FMfv5snc6mCNUU1hKXBLAZC0PS7nNvUEyUPIL94LDx0U6fmxUgcHgcpvzwq9igtt9nG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7543</t>
+          <t>FRCL-2026-7476</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1214,7 +1217,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1229,14 +1232,14 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuJqL36h/Obpu0k05p8tk7IWm3/x/7bKOxBUVoTcA5SCoAi3iJzVM8UjU8Gy38hSJfcBr/cHsbLG7clx134Llgq</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6PReqMK/LFFkCchf3WXUA2ag+a609SCwXUn4EtAJeAF7OhruCjorCePVpb3dei5tYtXFVhPYRX4eN80Ukmvyn/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7544</t>
+          <t>FRCL-2026-7477</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1246,7 +1249,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1261,14 +1264,14 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvkIoAmjHBWhI5xNONjN9YEHgNWXK/Xw2jYc0CVulG57HpZfUH64y3GfvOXo837V3uwWHG9IOH+29+As1Kf0MrU</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7gLgnQ/iiFa6Jcw39zjw8UGMLfR39RzlUvqfCnW4pMshOyMwy2NJ+zkWifRAY+SNt+Luu0//oeGPxeBdqasrs/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7559</t>
+          <t>FRCL-2026-7543</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1293,14 +1296,14 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4xATPb6L7Qx8GIgOuR09E99FdulkT+Xl0R01utj+4JD0gFi0sXUyUAmn3xM8fmjMLE2LXCFgWt1D+UloJik/FY</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuJqL36h/Obpu0k05p8tk7IWm3/x/7bKOxBUVoTcA5SCoAi3iJzVM8UjU8Gy38hSJfcBr/cHsbLG7clx134Llgq</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7614</t>
+          <t>FRCL-2026-7544</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1325,14 +1328,14 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7iD7qPRLGVgyxHLgDDQBezYUcholOOauNEzOprNCLEw/Lda9kYZzKGkeJrhqBRQdHrDs4dhgInPN2P4zvN3g5K</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvkIoAmjHBWhI5xNONjN9YEHgNWXK/Xw2jYc0CVulG57HpZfUH64y3GfvOXo837V3uwWHG9IOH+29+As1Kf0MrU</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7627</t>
+          <t>FRCL-2026-7559</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1342,7 +1345,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1357,14 +1360,14 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEz3dLbd4QiV3hetAg1x/5tCrNyvdv76iL7S7iW6hrSpMx0B5gRrbNEsOHRHpOhVwivZoF/HsLk9wJ6DO4qr/s1</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4xATPb6L7Qx8GIgOuR09E99FdulkT+Xl0R01utj+4JD0gFi0sXUyUAmn3xM8fmjMLE2LXCFgWt1D+UloJik/FY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7628</t>
+          <t>FRCL-2026-7614</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1374,7 +1377,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1389,14 +1392,14 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyFvqboZo8Pr2fm12+E+jyi/ZrpeyychtDdak9PyUZ9XrTLzJtEPVm3F2Pi6iLBjRyALgmeSCQ28nvlg1LFLOZql</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7iD7qPRLGVgyxHLgDDQBezYUcholOOauNEzOprNCLEw/Lda9kYZzKGkeJrhqBRQdHrDs4dhgInPN2P4zvN3g5K</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7621</t>
+          <t>FRCL-2026-7627</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1421,14 +1424,14 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jysdRNQpEB1hDuzfGy49nG35z/Zhl+GDIJFs3MEQ28RAXhkCtrGPg1M8KQdd+LBc87aScLKiEcyJXsViT86t15+D</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEz3dLbd4QiV3hetAg1x/5tCrNyvdv76iL7S7iW6hrSpMx0B5gRrbNEsOHRHpOhVwivZoF/HsLk9wJ6DO4qr/s1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7622</t>
+          <t>FRCL-2026-7628</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1453,14 +1456,14 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jys3T8xW8icUmFia0CD+JBdf805d1N57A8gPRzkxN6ZzG9V/a3UZp03R1nTxtu1g4mQWgPBkpZBNR38gebcl8bni</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyFvqboZo8Pr2fm12+E+jyi/ZrpeyychtDdak9PyUZ9XrTLzJtEPVm3F2Pi6iLBjRyALgmeSCQ28nvlg1LFLOZql</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7639</t>
+          <t>FRCL-2026-7621</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1485,14 +1488,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS1SQ44IftPUOeXtDGcEbB0EU0LAPCJOy+g461t4JdEYiFHXaFbGD58Yvkt5ZQpx4QG7MpLHMFVAtgJpFNeOMuy</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jysdRNQpEB1hDuzfGy49nG35z/Zhl+GDIJFs3MEQ28RAXhkCtrGPg1M8KQdd+LBc87aScLKiEcyJXsViT86t15+D</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7640</t>
+          <t>FRCL-2026-7622</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1517,14 +1520,14 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSjY3vMhVP+Xcc1KpbUWMQZcspSBoUbYtUA9xaEcRyXUkQ4CDqaBPhPE027DImKXKKn8CJS5mPntDKu6fBr0DVo</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jys3T8xW8icUmFia0CD+JBdf805d1N57A8gPRzkxN6ZzG9V/a3UZp03R1nTxtu1g4mQWgPBkpZBNR38gebcl8bni</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7649</t>
+          <t>FRCL-2026-7639</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1549,14 +1552,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTI8YP9ywg8e7M1cXE89bchaBb6zHPCLMRTqTA4/+/eYUtxtomPw+rX/v+OCWvHbAW7nUJE+vuAmetv/wf3tv3Z</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS1SQ44IftPUOeXtDGcEbB0EU0LAPCJOy+g461t4JdEYiFHXaFbGD58Yvkt5ZQpx4QG7MpLHMFVAtgJpFNeOMuy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7650</t>
+          <t>FRCL-2026-7640</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1581,14 +1584,14 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQcewt+2sIpU+KGhf4iMhlFLSKtnRpefg6fVEhTB/s/USLXiWvesYj2OkzQP2Xyi/iTLDFbuvjbhfZ9yaIHb1Uf</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSjY3vMhVP+Xcc1KpbUWMQZcspSBoUbYtUA9xaEcRyXUkQ4CDqaBPhPE027DImKXKKn8CJS5mPntDKu6fBr0DVo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7651</t>
+          <t>FRCL-2026-7649</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1613,14 +1616,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQL3uqSjem7KtfPi+nDhgP+3tPH4ZNBxAb4Ge+JTCdWsms/qSU2CRdAoP679MmVheOoQOmukE0z6nWolbio6s4K</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTI8YP9ywg8e7M1cXE89bchaBb6zHPCLMRTqTA4/+/eYUtxtomPw+rX/v+OCWvHbAW7nUJE+vuAmetv/wf3tv3Z</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7654</t>
+          <t>FRCL-2026-7650</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1645,14 +1648,14 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVReb8DtEbqsPg68R8vu0tAXwb0XCQyQqxv1ECBQCdeFH+F52PFz/EK1iJI07wb1IyMRyY6qXkGyf11q1Fn98mBv</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQcewt+2sIpU+KGhf4iMhlFLSKtnRpefg6fVEhTB/s/USLXiWvesYj2OkzQP2Xyi/iTLDFbuvjbhfZ9yaIHb1Uf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7756</t>
+          <t>FRCL-2026-7651</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1662,7 +1665,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1677,14 +1680,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7RyRMKjpG27qrRxBcDQq8JNwIQlcXxoi0jlxs/XK6FQbr4YmHsOlP4alB/cjCHT4ngQiDG9k5EdPHoiq3tgOhe</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQL3uqSjem7KtfPi+nDhgP+3tPH4ZNBxAb4Ge+JTCdWsms/qSU2CRdAoP679MmVheOoQOmukE0z6nWolbio6s4K</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7762</t>
+          <t>FRCL-2026-7654</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1694,7 +1697,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1709,14 +1712,14 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC74AlRJFmXW60+pXuQvgdDX5dOwUNV2S7GwYjvm2x255yUgWNrno/DWumxR51giPSa3Qm2iYpVG+/OJktxXC2T0</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVReb8DtEbqsPg68R8vu0tAXwb0XCQyQqxv1ECBQCdeFH+F52PFz/EK1iJI07wb1IyMRyY6qXkGyf11q1Fn98mBv</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7763</t>
+          <t>FRCL-2026-7756</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1741,14 +1744,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7SPaa6ekl5UN2duI/XORrn58ypEnhgOrJaJlR4EBC4HkbOJo4eDN1m4vM4IN0RiHBd0EM/owsZfviFztShOSme</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7RyRMKjpG27qrRxBcDQq8JNwIQlcXxoi0jlxs/XK6FQbr4YmHsOlP4alB/cjCHT4ngQiDG9k5EdPHoiq3tgOhe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7764</t>
+          <t>FRCL-2026-7762</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1773,14 +1776,14 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5J3iNGA2ZkldcU8Li9NVCRavga8mzTDfR/zJh2ufG/E8IJjg4bjEmt0vUX7a2Q1oZwIxWwq3G/LYOkKyxQRoDi</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC74AlRJFmXW60+pXuQvgdDX5dOwUNV2S7GwYjvm2x255yUgWNrno/DWumxR51giPSa3Qm2iYpVG+/OJktxXC2T0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7765</t>
+          <t>FRCL-2026-7763</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1805,14 +1808,14 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6zdDf6uiq3hn30j56s3jsSu7o6TJ/dM3toCMGB7ODysPqCjB9BPnG+ZBbmNXhvHC+m3HEqT6cqsZQF7wJwSzJa</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7SPaa6ekl5UN2duI/XORrn58ypEnhgOrJaJlR4EBC4HkbOJo4eDN1m4vM4IN0RiHBd0EM/owsZfviFztShOSme</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7766</t>
+          <t>FRCL-2026-7764</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1837,37 +1840,101 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC58Rzz0Due88sAHNlFFvP0ayFCHCzHp3Eq4vuDEByVJMkow+2VXAxf1U8uo7tXbeCLWld4XVhS+f1L389A3HDxe</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5J3iNGA2ZkldcU8Li9NVCRavga8mzTDfR/zJh2ufG/E8IJjg4bjEmt0vUX7a2Q1oZwIxWwq3G/LYOkKyxQRoDi</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>FRCL-2026-7765</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6zdDf6uiq3hn30j56s3jsSu7o6TJ/dM3toCMGB7ODysPqCjB9BPnG+ZBbmNXhvHC+m3HEqT6cqsZQF7wJwSzJa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7766</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC58Rzz0Due88sAHNlFFvP0ayFCHCzHp3Eq4vuDEByVJMkow+2VXAxf1U8uo7tXbeCLWld4XVhS+f1L389A3HDxe</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>FRCL-2026-7767</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2027</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>10/14/2026</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6FI/LukdRpLllLexuFK+QgjsinEvvcaDIVK0XF3jqjtSl81RmZzMX1lq8VN/6DvowPSNjUYBXxAXIWvOfegtEh</t>
         </is>

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/23/2026</t>
+          <t>10/24/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/24/2026</t>
+          <t>10/25/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/25/2026</t>
+          <t>10/26/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/26/2026</t>
+          <t>10/27/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/27/2026</t>
+          <t>10/28/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/28/2026</t>
+          <t>10/29/2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -500,17 +500,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7140</t>
+          <t>FRCL-2026-8130</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>04/06/2027</t>
+          <t>05/04/2027</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>10/29/2026</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -525,14 +525,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNHHz3SozCezeRI2vkUwy0uiwMMZgibq59cy5K785CrTEMyPDsOYmCTVP5hyJkJU1bO1o58n6s0lxLJ6oof59ghK</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSMx1+mqsiI0yfoQj3WpQnkw+gbH93VsF9ZnbR6tqZL4J6b1bVlrJ3O1i4tIyI7Z2yejN/mCLOJ9lajAd3aye7C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7828</t>
+          <t>FRCL-2026-7140</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -557,24 +557,24 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNEl7qNJ4CvE/0NueJ+S4zQbSfu2WEyrasTwYMPoMONyYc4iYReJs3flAKNtLYjrae3IOgaCjo1MuFMLICB8c3mH</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNHHz3SozCezeRI2vkUwy0uiwMMZgibq59cy5K785CrTEMyPDsOYmCTVP5hyJkJU1bO1o58n6s0lxLJ6oof59ghK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7052</t>
+          <t>FRCL-2026-7828</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>03/02/2027</t>
+          <t>04/06/2027</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>10/15/2026</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -589,14 +589,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyu7kQJKvj6WB4WOjyk7WprD5SOwNnavLkbHE46ioV+wWkcJDdPr+FVHUVabA40RI5HoTZAsK7vmoNl8pjS25eso</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NXW7+UCmLW1nhGEPTIdxiNEl7qNJ4CvE/0NueJ+S4zQbSfu2WEyrasTwYMPoMONyYc4iYReJs3flAKNtLYjrae3IOgaCjo1MuFMLICB8c3mH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7999</t>
+          <t>FRCL-2026-7052</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -621,24 +621,24 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvY/7ZQnmZIG+2sIB5azcMp4rDQLRo6h240EYwzj05BrPujAiTt2SEIXn5nu+fpZWF+gaf3Giwbf/fGZv4kbZ/T</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyu7kQJKvj6WB4WOjyk7WprD5SOwNnavLkbHE46ioV+wWkcJDdPr+FVHUVabA40RI5HoTZAsK7vmoNl8pjS25eso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-6803</t>
+          <t>FRCL-2026-7999</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/02/2027</t>
+          <t>03/02/2027</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>10/22/2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -653,24 +653,24 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqWQ0Frk50yWO27qHp80a9/7vLSfK1ixIiiQcszcEiu7i0N3bEcqRx7p7Bh4sZTvPfAu3gmsvPuIyNK99yeXoK</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvY/7ZQnmZIG+2sIB5azcMp4rDQLRo6h240EYwzj05BrPujAiTt2SEIXn5nu+fpZWF+gaf3Giwbf/fGZv4kbZ/T</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7815</t>
+          <t>FRCL-2026-8164</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>02/02/2027</t>
+          <t>03/02/2027</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026</t>
+          <t>10/29/2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -685,145 +685,147 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRbotgUHdJzWLhBp0DwBcc/+3Dk8F8qG7Mp5JbE6d2FihjiMuJ4dKRbeuzoh3/pOjF+4WTCacCWrYO/Db+V4OLw</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQ2T2275NN7yxVWupgTbDTy1mE8FNoSubYj7No8Qot9q6qrpN0VhkPyqILiUKCmO3V7UTg/bh/YqdIEXoeH6HkR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-6803</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2027</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>09/15/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqWQ0Frk50yWO27qHp80a9/7vLSfK1ixIiiQcszcEiu7i0N3bEcqRx7p7Bh4sZTvPfAu3gmsvPuIyNK99yeXoK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7815</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>02/02/2027</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRbotgUHdJzWLhBp0DwBcc/+3Dk8F8qG7Mp5JbE6d2FihjiMuJ4dKRbeuzoh3/pOjF+4WTCacCWrYO/Db+V4OLw</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-8084</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2027</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10/29/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6/azeC1VH2AB3oBu/XC7AQJDGBSZyvqVNXhp3hRvGABx8Q4uNF51IlZuv8FjJE2HZplM761wthw391scfgpa3J</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>1
 2
 3
-4</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+4
+5
+6</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2027/1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10/29/2026</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>https://www.cclerk.hctx.net/Applications/WebSearch/javascript:__doPostBack('ctl00$ContentPlaceHolder1$GridView1','Page$2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>FRCL-2026-4751</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>01/05/2027</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTvnvI5i1EaYEHYE9IUM9gBwJ81IYSOdvvwehObd3nXphm0Omf5bxwz05bsGeBZndJFBLgzPGCeA/BCFAIlY45+</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FRCL-2026-6402</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2027</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jytWfj882gWXL/+/9I5LXvTUb8ioTA8d7wWc2fNIo3Xtox7VOAa1k4RB0C48z7IRtD6dqDU25S5ILoKYYkZLOFIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>FRCL-2026-7181</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>01/05/2027</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSz8TQyjykaScwy4MXDzjWoI9O/eB/FRNb9gTzJHoJAi0liU1gyQd+nSZU5bwWbpC7wd4p0fGzxxsddPZ1OPhZr</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7408</t>
+          <t>FRCL-2026-4751</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -833,7 +835,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -848,14 +850,14 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS5tEjapY60kBilva8st2XiTrjq4OHpdP5I4sz742b41bO6fl/yLegtLra9/oMx6RpzyhzRLvTjdCy/RYosvObA</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTvnvI5i1EaYEHYE9IUM9gBwJ81IYSOdvvwehObd3nXphm0Omf5bxwz05bsGeBZndJFBLgzPGCeA/BCFAIlY45+</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7409</t>
+          <t>FRCL-2026-6402</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -865,7 +867,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -880,14 +882,14 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSxvmP9INW4q9N5y6gDYVU14NM5XruBd/g19nJu+XiIvN+BYhup340S3JRDCv1sbstvTADur/T5WfCjpEXdYkU9</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jytWfj882gWXL/+/9I5LXvTUb8ioTA8d7wWc2fNIo3Xtox7VOAa1k4RB0C48z7IRtD6dqDU25S5ILoKYYkZLOFIS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7410</t>
+          <t>FRCL-2026-7181</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -897,7 +899,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>09/29/2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -912,14 +914,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRIdL4OwFbCyUHSMpRz/cEzas+ndb/wm6JRRfCH2qiBI2sNbYfDi5Kz8gfzvPLqNSGZABPl4ImwnHgL5yd7nYmj</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSz8TQyjykaScwy4MXDzjWoI9O/eB/FRNb9gTzJHoJAi0liU1gyQd+nSZU5bwWbpC7wd4p0fGzxxsddPZ1OPhZr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7423</t>
+          <t>FRCL-2026-7408</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -944,14 +946,14 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqF2nHwQs4OGbG8NV0fSdm5Eim2T7qwwTliFofvDzStivCXpHpi4Os7YSk2P4bTgh7Bi5mwgBrE+iZgV6JNnZ5</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS5tEjapY60kBilva8st2XiTrjq4OHpdP5I4sz742b41bO6fl/yLegtLra9/oMx6RpzyhzRLvTjdCy/RYosvObA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7424</t>
+          <t>FRCL-2026-7409</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -976,14 +978,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuCBQTxEriTYJIKp3x9TacrZntm2B3XO44wXehJQQ7GEYjwzezChnqGn+KP3vp0MUVdKFmgBmuKNeTCFRWO97mz</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSxvmP9INW4q9N5y6gDYVU14NM5XruBd/g19nJu+XiIvN+BYhup340S3JRDCv1sbstvTADur/T5WfCjpEXdYkU9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7425</t>
+          <t>FRCL-2026-7410</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1008,14 +1010,14 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuG7uViEw7pLPVNcTN6jDDPepl6i/ph6p9jkYCFBD8/ibMRiRGtuFSorFjBj9JS8r/9KAuQIx1gkOUwZPjuUf30</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVRIdL4OwFbCyUHSMpRz/cEzas+ndb/wm6JRRfCH2qiBI2sNbYfDi5Kz8gfzvPLqNSGZABPl4ImwnHgL5yd7nYmj</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7426</t>
+          <t>FRCL-2026-7423</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1040,14 +1042,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyv+SWiDKaitm6RC0ggXxSGrJCOhGQefO8xMkjY+BuJcl1S0yCbHhM38IIEhg4xWzNsq6X1tj4zLkyv29b9ApNAO</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvqF2nHwQs4OGbG8NV0fSdm5Eim2T7qwwTliFofvDzStivCXpHpi4Os7YSk2P4bTgh7Bi5mwgBrE+iZgV6JNnZ5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7430</t>
+          <t>FRCL-2026-7424</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1072,14 +1074,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEFYQj99dHPPiUi1qvasfwHFWOixuTkN5HXVjxPgNzO0VEqYAQZciUwy5WShec7lCQ4L08Vpa7gGEhExB9BOm6S</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuCBQTxEriTYJIKp3x9TacrZntm2B3XO44wXehJQQ7GEYjwzezChnqGn+KP3vp0MUVdKFmgBmuKNeTCFRWO97mz</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7472</t>
+          <t>FRCL-2026-7425</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1104,14 +1106,14 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5bZnWnkDFllWSZ2E4Y+Hc48KO0Bly9KsxPNqC6YYFPpPRHVcRvJpER8e13zcb8ziafDm325KButdfUS++gHFQ2</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuG7uViEw7pLPVNcTN6jDDPepl6i/ph6p9jkYCFBD8/ibMRiRGtuFSorFjBj9JS8r/9KAuQIx1gkOUwZPjuUf30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7473</t>
+          <t>FRCL-2026-7426</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1136,14 +1138,14 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4awvONf5MaBdKV+k8h8tjZbmHo5Vne0P234XdqxQrSrrEVmerHY+Gv8bbZ5lpj0Hlbu7ZNGNoUhXNqjz0JKKOB</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyv+SWiDKaitm6RC0ggXxSGrJCOhGQefO8xMkjY+BuJcl1S0yCbHhM38IIEhg4xWzNsq6X1tj4zLkyv29b9ApNAO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7474</t>
+          <t>FRCL-2026-7430</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1168,14 +1170,14 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC76tl4EO6VaOT0w8CHAtQGs8gI0wm9LvYzHc1gEaXSsZcqiYkE/1oCJA2B8wrOIepaVROl51g+/S5oixeGJFBXb</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEFYQj99dHPPiUi1qvasfwHFWOixuTkN5HXVjxPgNzO0VEqYAQZciUwy5WShec7lCQ4L08Vpa7gGEhExB9BOm6S</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7475</t>
+          <t>FRCL-2026-7472</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1200,14 +1202,14 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5fKsOExZKATTOGO2Xa1FMfv5snc6mCNUU1hKXBLAZC0PS7nNvUEyUPIL94LDx0U6fmxUgcHgcpvzwq9igtt9nG</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5bZnWnkDFllWSZ2E4Y+Hc48KO0Bly9KsxPNqC6YYFPpPRHVcRvJpER8e13zcb8ziafDm325KButdfUS++gHFQ2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7476</t>
+          <t>FRCL-2026-7473</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1232,14 +1234,14 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6PReqMK/LFFkCchf3WXUA2ag+a609SCwXUn4EtAJeAF7OhruCjorCePVpb3dei5tYtXFVhPYRX4eN80Ukmvyn/</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4awvONf5MaBdKV+k8h8tjZbmHo5Vne0P234XdqxQrSrrEVmerHY+Gv8bbZ5lpj0Hlbu7ZNGNoUhXNqjz0JKKOB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7477</t>
+          <t>FRCL-2026-7474</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1264,14 +1266,14 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7gLgnQ/iiFa6Jcw39zjw8UGMLfR39RzlUvqfCnW4pMshOyMwy2NJ+zkWifRAY+SNt+Luu0//oeGPxeBdqasrs/</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC76tl4EO6VaOT0w8CHAtQGs8gI0wm9LvYzHc1gEaXSsZcqiYkE/1oCJA2B8wrOIepaVROl51g+/S5oixeGJFBXb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7543</t>
+          <t>FRCL-2026-7475</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1281,7 +1283,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1296,14 +1298,14 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuJqL36h/Obpu0k05p8tk7IWm3/x/7bKOxBUVoTcA5SCoAi3iJzVM8UjU8Gy38hSJfcBr/cHsbLG7clx134Llgq</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5fKsOExZKATTOGO2Xa1FMfv5snc6mCNUU1hKXBLAZC0PS7nNvUEyUPIL94LDx0U6fmxUgcHgcpvzwq9igtt9nG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7544</t>
+          <t>FRCL-2026-7476</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1313,7 +1315,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1328,14 +1330,14 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvkIoAmjHBWhI5xNONjN9YEHgNWXK/Xw2jYc0CVulG57HpZfUH64y3GfvOXo837V3uwWHG9IOH+29+As1Kf0MrU</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6PReqMK/LFFkCchf3WXUA2ag+a609SCwXUn4EtAJeAF7OhruCjorCePVpb3dei5tYtXFVhPYRX4eN80Ukmvyn/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7559</t>
+          <t>FRCL-2026-7477</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1345,7 +1347,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1360,14 +1362,14 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4xATPb6L7Qx8GIgOuR09E99FdulkT+Xl0R01utj+4JD0gFi0sXUyUAmn3xM8fmjMLE2LXCFgWt1D+UloJik/FY</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7gLgnQ/iiFa6Jcw39zjw8UGMLfR39RzlUvqfCnW4pMshOyMwy2NJ+zkWifRAY+SNt+Luu0//oeGPxeBdqasrs/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7614</t>
+          <t>FRCL-2026-7543</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1392,14 +1394,14 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7iD7qPRLGVgyxHLgDDQBezYUcholOOauNEzOprNCLEw/Lda9kYZzKGkeJrhqBRQdHrDs4dhgInPN2P4zvN3g5K</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyuJqL36h/Obpu0k05p8tk7IWm3/x/7bKOxBUVoTcA5SCoAi3iJzVM8UjU8Gy38hSJfcBr/cHsbLG7clx134Llgq</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7627</t>
+          <t>FRCL-2026-7544</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1409,7 +1411,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1424,14 +1426,14 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEz3dLbd4QiV3hetAg1x/5tCrNyvdv76iL7S7iW6hrSpMx0B5gRrbNEsOHRHpOhVwivZoF/HsLk9wJ6DO4qr/s1</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jyvkIoAmjHBWhI5xNONjN9YEHgNWXK/Xw2jYc0CVulG57HpZfUH64y3GfvOXo837V3uwWHG9IOH+29+As1Kf0MrU</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7628</t>
+          <t>FRCL-2026-7559</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1456,14 +1458,14 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyFvqboZo8Pr2fm12+E+jyi/ZrpeyychtDdak9PyUZ9XrTLzJtEPVm3F2Pi6iLBjRyALgmeSCQ28nvlg1LFLOZql</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC4xATPb6L7Qx8GIgOuR09E99FdulkT+Xl0R01utj+4JD0gFi0sXUyUAmn3xM8fmjMLE2LXCFgWt1D+UloJik/FY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7621</t>
+          <t>FRCL-2026-7614</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1473,7 +1475,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/12/2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1488,14 +1490,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jysdRNQpEB1hDuzfGy49nG35z/Zhl+GDIJFs3MEQ28RAXhkCtrGPg1M8KQdd+LBc87aScLKiEcyJXsViT86t15+D</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7iD7qPRLGVgyxHLgDDQBezYUcholOOauNEzOprNCLEw/Lda9kYZzKGkeJrhqBRQdHrDs4dhgInPN2P4zvN3g5K</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7622</t>
+          <t>FRCL-2026-7627</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1520,14 +1522,14 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jys3T8xW8icUmFia0CD+JBdf805d1N57A8gPRzkxN6ZzG9V/a3UZp03R1nTxtu1g4mQWgPBkpZBNR38gebcl8bni</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyEz3dLbd4QiV3hetAg1x/5tCrNyvdv76iL7S7iW6hrSpMx0B5gRrbNEsOHRHpOhVwivZoF/HsLk9wJ6DO4qr/s1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7639</t>
+          <t>FRCL-2026-7628</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1552,14 +1554,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS1SQ44IftPUOeXtDGcEbB0EU0LAPCJOy+g461t4JdEYiFHXaFbGD58Yvkt5ZQpx4QG7MpLHMFVAtgJpFNeOMuy</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NS3bRzpsleMPc8VGgBZ/oyFvqboZo8Pr2fm12+E+jyi/ZrpeyychtDdak9PyUZ9XrTLzJtEPVm3F2Pi6iLBjRyALgmeSCQ28nvlg1LFLOZql</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7640</t>
+          <t>FRCL-2026-7621</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1584,14 +1586,14 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSjY3vMhVP+Xcc1KpbUWMQZcspSBoUbYtUA9xaEcRyXUkQ4CDqaBPhPE027DImKXKKn8CJS5mPntDKu6fBr0DVo</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jysdRNQpEB1hDuzfGy49nG35z/Zhl+GDIJFs3MEQ28RAXhkCtrGPg1M8KQdd+LBc87aScLKiEcyJXsViT86t15+D</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7649</t>
+          <t>FRCL-2026-7622</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1616,14 +1618,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTI8YP9ywg8e7M1cXE89bchaBb6zHPCLMRTqTA4/+/eYUtxtomPw+rX/v+OCWvHbAW7nUJE+vuAmetv/wf3tv3Z</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NSvzTel3b4phRC1xP2A+jys3T8xW8icUmFia0CD+JBdf805d1N57A8gPRzkxN6ZzG9V/a3UZp03R1nTxtu1g4mQWgPBkpZBNR38gebcl8bni</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7650</t>
+          <t>FRCL-2026-7639</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1648,14 +1650,14 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQcewt+2sIpU+KGhf4iMhlFLSKtnRpefg6fVEhTB/s/USLXiWvesYj2OkzQP2Xyi/iTLDFbuvjbhfZ9yaIHb1Uf</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVS1SQ44IftPUOeXtDGcEbB0EU0LAPCJOy+g461t4JdEYiFHXaFbGD58Yvkt5ZQpx4QG7MpLHMFVAtgJpFNeOMuy</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7651</t>
+          <t>FRCL-2026-7640</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1680,14 +1682,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQL3uqSjem7KtfPi+nDhgP+3tPH4ZNBxAb4Ge+JTCdWsms/qSU2CRdAoP679MmVheOoQOmukE0z6nWolbio6s4K</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVSjY3vMhVP+Xcc1KpbUWMQZcspSBoUbYtUA9xaEcRyXUkQ4CDqaBPhPE027DImKXKKn8CJS5mPntDKu6fBr0DVo</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7654</t>
+          <t>FRCL-2026-7649</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1712,14 +1714,14 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVReb8DtEbqsPg68R8vu0tAXwb0XCQyQqxv1ECBQCdeFH+F52PFz/EK1iJI07wb1IyMRyY6qXkGyf11q1Fn98mBv</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVTI8YP9ywg8e7M1cXE89bchaBb6zHPCLMRTqTA4/+/eYUtxtomPw+rX/v+OCWvHbAW7nUJE+vuAmetv/wf3tv3Z</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7756</t>
+          <t>FRCL-2026-7650</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1729,7 +1731,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1744,14 +1746,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7RyRMKjpG27qrRxBcDQq8JNwIQlcXxoi0jlxs/XK6FQbr4YmHsOlP4alB/cjCHT4ngQiDG9k5EdPHoiq3tgOhe</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQcewt+2sIpU+KGhf4iMhlFLSKtnRpefg6fVEhTB/s/USLXiWvesYj2OkzQP2Xyi/iTLDFbuvjbhfZ9yaIHb1Uf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7762</t>
+          <t>FRCL-2026-7651</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1761,7 +1763,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1776,14 +1778,14 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC74AlRJFmXW60+pXuQvgdDX5dOwUNV2S7GwYjvm2x255yUgWNrno/DWumxR51giPSa3Qm2iYpVG+/OJktxXC2T0</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVQL3uqSjem7KtfPi+nDhgP+3tPH4ZNBxAb4Ge+JTCdWsms/qSU2CRdAoP679MmVheOoQOmukE0z6nWolbio6s4K</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7763</t>
+          <t>FRCL-2026-7654</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1793,7 +1795,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1808,14 +1810,14 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7SPaa6ekl5UN2duI/XORrn58ypEnhgOrJaJlR4EBC4HkbOJo4eDN1m4vM4IN0RiHBd0EM/owsZfviFztShOSme</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NdRpQgMQd0Nsa06X5vPrNVReb8DtEbqsPg68R8vu0tAXwb0XCQyQqxv1ECBQCdeFH+F52PFz/EK1iJI07wb1IyMRyY6qXkGyf11q1Fn98mBv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7764</t>
+          <t>FRCL-2026-7756</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1840,14 +1842,14 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5J3iNGA2ZkldcU8Li9NVCRavga8mzTDfR/zJh2ufG/E8IJjg4bjEmt0vUX7a2Q1oZwIxWwq3G/LYOkKyxQRoDi</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7RyRMKjpG27qrRxBcDQq8JNwIQlcXxoi0jlxs/XK6FQbr4YmHsOlP4alB/cjCHT4ngQiDG9k5EdPHoiq3tgOhe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FRCL-2026-7765</t>
+          <t>FRCL-2026-7762</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1872,14 +1874,14 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6zdDf6uiq3hn30j56s3jsSu7o6TJ/dM3toCMGB7ODysPqCjB9BPnG+ZBbmNXhvHC+m3HEqT6cqsZQF7wJwSzJa</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC74AlRJFmXW60+pXuQvgdDX5dOwUNV2S7GwYjvm2x255yUgWNrno/DWumxR51giPSa3Qm2iYpVG+/OJktxXC2T0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>FRCL-2026-7766</t>
+          <t>FRCL-2026-7763</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1904,37 +1906,133 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC58Rzz0Due88sAHNlFFvP0ayFCHCzHp3Eq4vuDEByVJMkow+2VXAxf1U8uo7tXbeCLWld4XVhS+f1L389A3HDxe</t>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC7SPaa6ekl5UN2duI/XORrn58ypEnhgOrJaJlR4EBC4HkbOJo4eDN1m4vM4IN0RiHBd0EM/owsZfviFztShOSme</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>FRCL-2026-7764</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC5J3iNGA2ZkldcU8Li9NVCRavga8mzTDfR/zJh2ufG/E8IJjg4bjEmt0vUX7a2Q1oZwIxWwq3G/LYOkKyxQRoDi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7765</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6zdDf6uiq3hn30j56s3jsSu7o6TJ/dM3toCMGB7ODysPqCjB9BPnG+ZBbmNXhvHC+m3HEqT6cqsZQF7wJwSzJa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>FRCL-2026-7766</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC58Rzz0Due88sAHNlFFvP0ayFCHCzHp3Eq4vuDEByVJMkow+2VXAxf1U8uo7tXbeCLWld4XVhS+f1L389A3HDxe</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>FRCL-2026-7767</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2027</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>10/14/2026</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Harris County (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Notice of Foreclosure Sale</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Harris County (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Foreclosure Sale</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>https://www.cclerk.hctx.net/Applications/WebSearch/ViewECdocs.aspx?ID=bWXqGXasMeuE7YZXR3B2NUNXeLVZTKlhHSbKofnpRC6FI/LukdRpLllLexuFK+QgjsinEvvcaDIVK0XF3jqjtSl81RmZzMX1lq8VN/6DvowPSNjUYBXxAXIWvOfegtEh</t>
         </is>

--- a/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
+++ b/reports/Harris_County_ALL_ACTIVE_NOTICES_MASTER.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
